--- a/feedback_forms/005_tenant_complaint_resolution_survey--feedback_forms.xlsx
+++ b/feedback_forms/005_tenant_complaint_resolution_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'name':_'maintenance_issue',_'label':_'maintenance_issue'}</t>
+          <t>maintenance_issue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'name': 'maintenance_issue', 'label': 'Maintenance Issue'}</t>
+          <t>Maintenance Issue</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'name':_'rent_issue',_'label':_'rent_issue'}</t>
+          <t>rent_issue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'name': 'rent_issue', 'label': 'Rent Issue'}</t>
+          <t>Rent Issue</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'name':_'follow_up_email',_'label':_'send_email'}</t>
+          <t>send_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'name': 'follow_up_email', 'label': 'Send Email'}</t>
+          <t>Send Email</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'name':_'follow_up_phone',_'label':_'call'}</t>
+          <t>call</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'name': 'follow_up_phone', 'label': 'Call'}</t>
+          <t>Call</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_8.3,_'name':_'follow_up_no_action',_'label':_'no_follow-up'}</t>
+          <t>no_follow-up</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 8.3, 'name': 'follow_up_no_action', 'label': 'No Follow-Up'}</t>
+          <t>No Follow-Up</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'name':_'contact_person',_'label':_'maintenance_person'}</t>
+          <t>maintenance_person</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'name': 'contact_person', 'label': 'Maintenance Person'}</t>
+          <t>Maintenance Person</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'name':_'contact_manager',_'label':_'property_manager'}</t>
+          <t>property_manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'name': 'contact_manager', 'label': 'Property Manager'}</t>
+          <t>Property Manager</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_13.1,_'name':_'satisfied',_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 13.1, 'name': 'satisfied', 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_13.2,_'name':_'not_satisfied',_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 13.2, 'name': 'not_satisfied', 'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_14.1,_'name':_'resolved',_'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 14.1, 'name': 'resolved', 'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_14.2,_'name':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 14.2, 'name': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_14.3,_'name':_'unresolved',_'label':_'unresolved'}</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 14.3, 'name': 'unresolved', 'label': 'Unresolved'}</t>
+          <t>Unresolved</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'name':_'maintenance_person',_'label':_'maintenance_person'}</t>
+          <t>maintenance_person</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'name': 'maintenance_person', 'label': 'Maintenance Person'}</t>
+          <t>Maintenance Person</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'name':_'property_manager',_'label':_'property_manager'}</t>
+          <t>property_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'name': 'property_manager', 'label': 'Property Manager'}</t>
+          <t>Property Manager</t>
         </is>
       </c>
     </row>
